--- a/results/Int Task Remove ACC -0.9/Rando_2_permute.xlsx
+++ b/results/Int Task Remove ACC -0.9/Rando_2_permute.xlsx
@@ -440,67 +440,67 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7015892160216712</v>
+        <v>0.7100837109285001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6991820904692421</v>
+        <v>0.7198343933924919</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6991820904692421</v>
+        <v>0.7231796887545294</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6961853579183277</v>
+        <v>0.7229341064434376</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7018234530234377</v>
+        <v>0.7214391437607781</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7018234530234377</v>
+        <v>0.716467629214346</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6910293511879412</v>
+        <v>0.7154242098428413</v>
       </c>
     </row>
     <row r="9">
@@ -510,417 +510,417 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6798142511048586</v>
+        <v>0.7181006555843358</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6806494404144354</v>
+        <v>0.7186642556429823</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6813046756637879</v>
+        <v>0.7125395340394189</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6928355244325599</v>
+        <v>0.7103802598599466</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6928355244325599</v>
+        <v>0.7103802598599466</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6878503955149374</v>
+        <v>0.7024776410134678</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.673325083257116</v>
+        <v>0.6931638402301178</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6720360815745194</v>
+        <v>0.6931638402301178</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6605731301184798</v>
+        <v>0.6885035362456451</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.656916624194483</v>
+        <v>0.6867980744391926</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6691796817728006</v>
+        <v>0.664877191390132</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6684474729632552</v>
+        <v>0.6822430200166165</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6684474729632552</v>
+        <v>0.6828348960769666</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6681690765267295</v>
+        <v>0.6392669882916409</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6629451724836104</v>
+        <v>0.6368315867375079</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6609239619914684</v>
+        <v>0.6643011987628377</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6696945842729577</v>
+        <v>0.667679308250309</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6737324671335116</v>
+        <v>0.6744004440379527</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6783362191145772</v>
+        <v>0.6604750368286195</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7070031976317976</v>
+        <v>0.6648592134384316</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7014284617156901</v>
+        <v>0.6415791623321767</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6868069761434326</v>
+        <v>0.6663960664939852</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6817913021622414</v>
+        <v>0.6242292171387479</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6751052495618965</v>
+        <v>0.6065080185155448</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6751052495618965</v>
+        <v>0.6027417249059212</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6751052495618965</v>
+        <v>0.6027417249059212</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6751052495618965</v>
+        <v>0.6371056195935237</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.664519377788328</v>
+        <v>0.6146279436714119</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6632982734184638</v>
+        <v>0.6329998394202373</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6334475427805433</v>
+        <v>0.6227387925798187</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6301350615439395</v>
+        <v>0.6170678833492749</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.641504108747408</v>
+        <v>0.6152571719809259</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6749661386152439</v>
+        <v>0.6141435862348235</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6977426325306673</v>
+        <v>0.6037987586486165</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7111079305457617</v>
+        <v>0.6160131186684447</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7147972505951924</v>
+        <v>0.6347822747868828</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7073110918725695</v>
+        <v>0.6489408717386599</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.7264616249275646</v>
+        <v>0.6573460005166479</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7310948747128765</v>
+        <v>0.6567541244562979</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7197949466246832</v>
+        <v>0.6504630631637006</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7047287249268663</v>
+        <v>0.7147002045646543</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6768981575217655</v>
+        <v>0.7029068427924122</v>
       </c>
     </row>
     <row r="51">
@@ -930,157 +930,157 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6760980513994875</v>
+        <v>0.7048556178480916</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6758547381502608</v>
+        <v>0.7044742409115345</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6587706222814893</v>
+        <v>0.7044742409115345</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6588498649035475</v>
+        <v>0.7040555117258136</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6348636119275854</v>
+        <v>0.7123066933834157</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6375433739902675</v>
+        <v>0.7142203852517961</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.6168718713127744</v>
+        <v>0.5282911869637159</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6125884061411286</v>
+        <v>0.5144392624501679</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6327495444421948</v>
+        <v>0.51482290844859</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.632124854256411</v>
+        <v>0.5083496240339033</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6251604052195405</v>
+        <v>0.5088713337196556</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6308845501323037</v>
+        <v>0.5088713337196556</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6581323177245149</v>
+        <v>0.5104387318387779</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.659868324594536</v>
+        <v>0.5053574296067193</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.6766003867877763</v>
+        <v>0.5092900629053766</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6813409806536295</v>
+        <v>0.5050439499828948</v>
       </c>
     </row>
     <row r="67">
@@ -1090,67 +1090,67 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6718007973134308</v>
+        <v>0.5052895322939867</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6800474408473026</v>
+        <v>0.5052895322939867</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6783091649154164</v>
+        <v>0.5033407572383074</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6802907540965294</v>
+        <v>0.5027839643652561</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7013696406504178</v>
+        <v>0.5016352954318548</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7031498069551982</v>
+        <v>0.502192088304906</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6914187571126362</v>
+        <v>0.503619153674833</v>
       </c>
     </row>
     <row r="74">
@@ -1160,147 +1160,147 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6667366003169705</v>
+        <v>0.5008351893095768</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6143132422450447</v>
+        <v>0.5011135857461024</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6103296423260327</v>
+        <v>0.5002783964365256</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5833297261067786</v>
+        <v>0.5008351893095768</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5862212090957963</v>
+        <v>0.5008351893095768</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5584562699415629</v>
+        <v>0.5005567928730512</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5678515824088362</v>
+        <v>0.5005567928730512</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5678515824088362</v>
+        <v>0.5010785025588036</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5555342418889766</v>
+        <v>0.5005567928730512</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5363023716932787</v>
+        <v>0.5002433132492268</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5233015199223632</v>
+        <v>0.5002433132492268</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5409682610608039</v>
+        <v>0.5002433132492268</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.519390355439814</v>
+        <v>0.5002433132492268</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5158764513268775</v>
+        <v>0.5005567928730512</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5091010325976918</v>
+        <v>0.5005567928730512</v>
       </c>
     </row>
     <row r="89">
@@ -1310,17 +1310,17 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5016307573081247</v>
+        <v>0.5005545238111861</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5002059610000629</v>
+        <v>0.5005545238111861</v>
       </c>
     </row>
   </sheetData>
